--- a/data-source/COMPRABASES.xlsx
+++ b/data-source/COMPRABASES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="8_{4387A5D2-32EA-4489-B23A-44C699D43E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1942F4B9-61D1-43CD-BBAB-872A77F2109E}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="8_{4387A5D2-32EA-4489-B23A-44C699D43E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{521F6FB8-8B4C-4D5D-906F-728BE9C113A0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="55">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -271,10 +271,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -597,7 +593,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -638,22 +634,22 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="B2" s="1">
-        <v>30099</v>
+        <v>9091</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
-        <v>45</v>
+      <c r="E2" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F2" s="5">
-        <v>30109</v>
+        <v>3356</v>
       </c>
       <c r="G2" s="3">
         <v>1.23</v>
@@ -664,91 +660,91 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>1357</v>
+        <v>1348</v>
       </c>
       <c r="B3" s="1">
-        <v>13485</v>
+        <v>30099</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
-        <v>45</v>
+      <c r="E3" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F3" s="5">
-        <v>12298</v>
+        <v>17467</v>
       </c>
       <c r="G3" s="3">
-        <v>1.75</v>
+        <v>1.23</v>
       </c>
       <c r="H3" s="4">
-        <v>46275</v>
+        <v>46176</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>1357</v>
+        <v>1348</v>
       </c>
       <c r="B4" s="1">
-        <v>13486</v>
+        <v>30105</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
-        <v>45</v>
+      <c r="E4" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F4" s="5">
-        <v>14386</v>
+        <v>2377</v>
       </c>
       <c r="G4" s="3">
-        <v>1.75</v>
+        <v>1.23</v>
       </c>
       <c r="H4" s="4">
-        <v>46275</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>1357</v>
+        <v>1348</v>
       </c>
       <c r="B5" s="1">
-        <v>30101</v>
+        <v>30117</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
-        <v>45</v>
+      <c r="E5" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F5" s="5">
-        <v>590</v>
+        <v>7098</v>
       </c>
       <c r="G5" s="3">
-        <v>1.75</v>
+        <v>1.23</v>
       </c>
       <c r="H5" s="4">
-        <v>46275</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>1357</v>
+        <v>1349</v>
       </c>
       <c r="B6" s="1">
-        <v>30102</v>
+        <v>30099</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1">
         <v>13</v>
@@ -757,13 +753,13 @@
         <v>45</v>
       </c>
       <c r="F6" s="5">
-        <v>2080</v>
+        <v>30109</v>
       </c>
       <c r="G6" s="3">
-        <v>1.75</v>
+        <v>1.23</v>
       </c>
       <c r="H6" s="4">
-        <v>46275</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -771,10 +767,10 @@
         <v>1357</v>
       </c>
       <c r="B7" s="1">
-        <v>30103</v>
+        <v>13485</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1">
         <v>13</v>
@@ -783,13 +779,13 @@
         <v>45</v>
       </c>
       <c r="F7" s="5">
-        <v>415</v>
+        <v>12298</v>
       </c>
       <c r="G7" s="3">
         <v>1.75</v>
       </c>
       <c r="H7" s="4">
-        <v>46183</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -797,36 +793,36 @@
         <v>1357</v>
       </c>
       <c r="B8" s="1">
-        <v>30099</v>
+        <v>13486</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D8" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
         <v>45</v>
       </c>
       <c r="F8" s="5">
-        <v>750</v>
+        <v>14386</v>
       </c>
       <c r="G8" s="3">
         <v>1.75</v>
       </c>
       <c r="H8" s="4">
-        <v>46184</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="B9" s="1">
-        <v>30103</v>
+        <v>30101</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="1">
         <v>13</v>
@@ -835,7 +831,7 @@
         <v>45</v>
       </c>
       <c r="F9" s="5">
-        <v>200</v>
+        <v>590</v>
       </c>
       <c r="G9" s="3">
         <v>1.75</v>
@@ -846,13 +842,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="B10" s="1">
-        <v>30104</v>
+        <v>30102</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" s="1">
         <v>13</v>
@@ -861,7 +857,7 @@
         <v>45</v>
       </c>
       <c r="F10" s="5">
-        <v>17901</v>
+        <v>2080</v>
       </c>
       <c r="G10" s="3">
         <v>1.75</v>
@@ -872,13 +868,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="B11" s="1">
-        <v>30105</v>
+        <v>30103</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1">
         <v>13</v>
@@ -887,39 +883,39 @@
         <v>45</v>
       </c>
       <c r="F11" s="5">
-        <v>1510</v>
+        <v>415</v>
       </c>
       <c r="G11" s="3">
         <v>1.75</v>
       </c>
       <c r="H11" s="4">
-        <v>46275</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="B12" s="1">
-        <v>30106</v>
+        <v>30099</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D12" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" t="s">
         <v>45</v>
       </c>
       <c r="F12" s="5">
-        <v>8172</v>
+        <v>750</v>
       </c>
       <c r="G12" s="3">
         <v>1.75</v>
       </c>
       <c r="H12" s="4">
-        <v>46275</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -927,10 +923,10 @@
         <v>1358</v>
       </c>
       <c r="B13" s="1">
-        <v>30107</v>
+        <v>30103</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D13" s="1">
         <v>13</v>
@@ -939,7 +935,7 @@
         <v>45</v>
       </c>
       <c r="F13" s="5">
-        <v>2250</v>
+        <v>200</v>
       </c>
       <c r="G13" s="3">
         <v>1.75</v>
@@ -950,13 +946,13 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="B14" s="1">
-        <v>30107</v>
+        <v>30104</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D14" s="1">
         <v>13</v>
@@ -965,7 +961,7 @@
         <v>45</v>
       </c>
       <c r="F14" s="5">
-        <v>13438</v>
+        <v>17901</v>
       </c>
       <c r="G14" s="3">
         <v>1.75</v>
@@ -976,13 +972,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="B15" s="1">
-        <v>30108</v>
+        <v>30105</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D15" s="1">
         <v>13</v>
@@ -991,7 +987,7 @@
         <v>45</v>
       </c>
       <c r="F15" s="5">
-        <v>8038</v>
+        <v>1510</v>
       </c>
       <c r="G15" s="3">
         <v>1.75</v>
@@ -1002,13 +998,13 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="B16" s="1">
-        <v>30109</v>
+        <v>30106</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D16" s="1">
         <v>13</v>
@@ -1017,7 +1013,7 @@
         <v>45</v>
       </c>
       <c r="F16" s="5">
-        <v>5434</v>
+        <v>8172</v>
       </c>
       <c r="G16" s="3">
         <v>1.75</v>
@@ -1028,13 +1024,13 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="B17" s="1">
-        <v>30110</v>
+        <v>30107</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D17" s="1">
         <v>13</v>
@@ -1043,7 +1039,7 @@
         <v>45</v>
       </c>
       <c r="F17" s="5">
-        <v>3785</v>
+        <v>2250</v>
       </c>
       <c r="G17" s="3">
         <v>1.75</v>
@@ -1054,13 +1050,13 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="B18" s="1">
-        <v>9091</v>
+        <v>30107</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D18" s="1">
         <v>13</v>
@@ -1069,7 +1065,7 @@
         <v>45</v>
       </c>
       <c r="F18" s="5">
-        <v>11730</v>
+        <v>13438</v>
       </c>
       <c r="G18" s="3">
         <v>1.75</v>
@@ -1080,13 +1076,13 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="B19" s="1">
-        <v>30099</v>
+        <v>30108</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D19" s="1">
         <v>13</v>
@@ -1095,7 +1091,7 @@
         <v>45</v>
       </c>
       <c r="F19" s="5">
-        <v>5395</v>
+        <v>8083</v>
       </c>
       <c r="G19" s="3">
         <v>1.75</v>
@@ -1106,13 +1102,13 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="B20" s="1">
-        <v>30110</v>
+        <v>30109</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D20" s="1">
         <v>13</v>
@@ -1121,7 +1117,7 @@
         <v>45</v>
       </c>
       <c r="F20" s="5">
-        <v>2727</v>
+        <v>5434</v>
       </c>
       <c r="G20" s="3">
         <v>1.75</v>
@@ -1132,13 +1128,13 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="B21" s="1">
-        <v>30111</v>
+        <v>30110</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D21" s="1">
         <v>13</v>
@@ -1147,7 +1143,7 @@
         <v>45</v>
       </c>
       <c r="F21" s="5">
-        <v>7691</v>
+        <v>3785</v>
       </c>
       <c r="G21" s="3">
         <v>1.75</v>
@@ -1161,10 +1157,10 @@
         <v>1361</v>
       </c>
       <c r="B22" s="1">
-        <v>30113</v>
+        <v>9091</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D22" s="1">
         <v>13</v>
@@ -1173,7 +1169,7 @@
         <v>45</v>
       </c>
       <c r="F22" s="5">
-        <v>443</v>
+        <v>11730</v>
       </c>
       <c r="G22" s="3">
         <v>1.75</v>
@@ -1187,10 +1183,10 @@
         <v>1361</v>
       </c>
       <c r="B23" s="1">
-        <v>30118</v>
+        <v>30099</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D23" s="1">
         <v>13</v>
@@ -1199,7 +1195,7 @@
         <v>45</v>
       </c>
       <c r="F23" s="5">
-        <v>2750</v>
+        <v>5395</v>
       </c>
       <c r="G23" s="3">
         <v>1.75</v>
@@ -1210,13 +1206,13 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>1471</v>
+        <v>1361</v>
       </c>
       <c r="B24" s="1">
-        <v>30099</v>
+        <v>30110</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D24" s="1">
         <v>13</v>
@@ -1225,24 +1221,24 @@
         <v>45</v>
       </c>
       <c r="F24" s="5">
-        <v>10111</v>
+        <v>2727</v>
       </c>
       <c r="G24" s="3">
         <v>1.75</v>
       </c>
       <c r="H24" s="4">
-        <v>46296</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>1471</v>
+        <v>1361</v>
       </c>
       <c r="B25" s="1">
-        <v>30107</v>
+        <v>30111</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D25" s="1">
         <v>13</v>
@@ -1251,24 +1247,24 @@
         <v>45</v>
       </c>
       <c r="F25" s="5">
-        <v>10128</v>
+        <v>7691</v>
       </c>
       <c r="G25" s="3">
         <v>1.75</v>
       </c>
       <c r="H25" s="4">
-        <v>46296</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>1471</v>
+        <v>1361</v>
       </c>
       <c r="B26" s="1">
-        <v>30114</v>
+        <v>30113</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D26" s="1">
         <v>13</v>
@@ -1277,24 +1273,24 @@
         <v>45</v>
       </c>
       <c r="F26" s="5">
-        <v>10103</v>
+        <v>443</v>
       </c>
       <c r="G26" s="3">
         <v>1.75</v>
       </c>
       <c r="H26" s="4">
-        <v>46296</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>1530</v>
+        <v>1361</v>
       </c>
       <c r="B27" s="1">
-        <v>30099</v>
+        <v>30118</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D27" s="1">
         <v>13</v>
@@ -1303,24 +1299,24 @@
         <v>45</v>
       </c>
       <c r="F27" s="5">
-        <v>15000</v>
+        <v>2750</v>
       </c>
       <c r="G27" s="3">
         <v>1.75</v>
       </c>
       <c r="H27" s="4">
-        <v>46217</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>1530</v>
+        <v>1471</v>
       </c>
       <c r="B28" s="1">
-        <v>30114</v>
+        <v>30099</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D28" s="1">
         <v>13</v>
@@ -1329,24 +1325,24 @@
         <v>45</v>
       </c>
       <c r="F28" s="5">
-        <v>15000</v>
+        <v>10111</v>
       </c>
       <c r="G28" s="3">
         <v>1.75</v>
       </c>
       <c r="H28" s="4">
-        <v>46217</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>1581</v>
+        <v>1471</v>
       </c>
       <c r="B29" s="1">
-        <v>9091</v>
+        <v>30107</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D29" s="1">
         <v>13</v>
@@ -1355,24 +1351,24 @@
         <v>45</v>
       </c>
       <c r="F29" s="5">
-        <v>30000</v>
+        <v>10128</v>
       </c>
       <c r="G29" s="3">
         <v>1.75</v>
       </c>
       <c r="H29" s="4">
-        <v>46324</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>1581</v>
+        <v>1471</v>
       </c>
       <c r="B30" s="1">
-        <v>13485</v>
+        <v>30114</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D30" s="1">
         <v>13</v>
@@ -1381,143 +1377,143 @@
         <v>45</v>
       </c>
       <c r="F30" s="5">
-        <v>25000</v>
+        <v>10103</v>
       </c>
       <c r="G30" s="3">
         <v>1.75</v>
       </c>
       <c r="H30" s="4">
-        <v>46324</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>1581</v>
+        <v>1530</v>
       </c>
       <c r="B31" s="1">
-        <v>14730</v>
+        <v>30099</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D31" s="1">
         <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F31" s="5">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="G31" s="3">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="H31" s="4">
-        <v>46324</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>1612</v>
+        <v>1530</v>
       </c>
       <c r="B32" s="1">
-        <v>8925</v>
+        <v>30114</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D32" s="1">
         <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F32" s="5">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="G32" s="3">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="H32" s="4">
-        <v>46332</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <v>1612</v>
+        <v>1581</v>
       </c>
       <c r="B33" s="1">
-        <v>30161</v>
+        <v>9091</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D33" s="1">
         <v>13</v>
       </c>
       <c r="E33" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F33" s="5">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="G33" s="3">
-        <v>2.44</v>
+        <v>1.75</v>
       </c>
       <c r="H33" s="4">
-        <v>46332</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <v>1612</v>
+        <v>1581</v>
       </c>
       <c r="B34" s="1">
-        <v>30162</v>
+        <v>13485</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D34" s="1">
         <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F34" s="5">
-        <v>3000</v>
+        <v>25000</v>
       </c>
       <c r="G34" s="3">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="H34" s="4">
-        <v>46332</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <v>1612</v>
+        <v>1581</v>
       </c>
       <c r="B35" s="1">
-        <v>30163</v>
+        <v>14730</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D35" s="1">
         <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F35" s="5">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="G35" s="3">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="H35" s="4">
-        <v>46332</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -1525,10 +1521,10 @@
         <v>1612</v>
       </c>
       <c r="B36" s="1">
-        <v>30164</v>
+        <v>8925</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D36" s="1">
         <v>13</v>
@@ -1537,7 +1533,7 @@
         <v>47</v>
       </c>
       <c r="F36" s="5">
-        <v>3000</v>
+        <v>7000</v>
       </c>
       <c r="G36" s="3">
         <v>2.6</v>
@@ -1551,10 +1547,10 @@
         <v>1612</v>
       </c>
       <c r="B37" s="1">
-        <v>30165</v>
+        <v>30161</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D37" s="1">
         <v>13</v>
@@ -1566,7 +1562,7 @@
         <v>3000</v>
       </c>
       <c r="G37" s="3">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="H37" s="4">
         <v>46332</v>
@@ -1577,10 +1573,10 @@
         <v>1612</v>
       </c>
       <c r="B38" s="1">
-        <v>30166</v>
+        <v>30162</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D38" s="1">
         <v>13</v>
@@ -1589,7 +1585,7 @@
         <v>47</v>
       </c>
       <c r="F38" s="5">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="G38" s="3">
         <v>2.6</v>
@@ -1600,25 +1596,25 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="B39" s="1">
-        <v>12494</v>
+        <v>30163</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D39" s="1">
         <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F39" s="5">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="G39" s="3">
-        <v>2.5099999999999998</v>
+        <v>2.44</v>
       </c>
       <c r="H39" s="4">
         <v>46332</v>
@@ -1626,25 +1622,25 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="B40" s="1">
-        <v>12495</v>
+        <v>30164</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D40" s="1">
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F40" s="5">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G40" s="3">
-        <v>2.5099999999999998</v>
+        <v>2.6</v>
       </c>
       <c r="H40" s="4">
         <v>46332</v>
@@ -1652,25 +1648,25 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="B41" s="1">
-        <v>30167</v>
+        <v>30165</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D41" s="1">
         <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F41" s="5">
         <v>3000</v>
       </c>
       <c r="G41" s="3">
-        <v>2.5099999999999998</v>
+        <v>2.6</v>
       </c>
       <c r="H41" s="4">
         <v>46332</v>
@@ -1678,25 +1674,25 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="B42" s="1">
-        <v>30168</v>
+        <v>30166</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D42" s="1">
         <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F42" s="5">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G42" s="3">
-        <v>2.5099999999999998</v>
+        <v>2.6</v>
       </c>
       <c r="H42" s="4">
         <v>46332</v>
@@ -1707,10 +1703,10 @@
         <v>1614</v>
       </c>
       <c r="B43" s="1">
-        <v>30169</v>
+        <v>12494</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D43" s="1">
         <v>13</v>
@@ -1719,7 +1715,7 @@
         <v>48</v>
       </c>
       <c r="F43" s="5">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="G43" s="3">
         <v>2.5099999999999998</v>
@@ -1733,10 +1729,10 @@
         <v>1614</v>
       </c>
       <c r="B44" s="1">
-        <v>30170</v>
+        <v>12495</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D44" s="1">
         <v>13</v>
@@ -1745,7 +1741,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="5">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G44" s="3">
         <v>2.5099999999999998</v>
@@ -1759,10 +1755,10 @@
         <v>1614</v>
       </c>
       <c r="B45" s="1">
-        <v>30171</v>
+        <v>30167</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D45" s="1">
         <v>13</v>
@@ -1785,10 +1781,10 @@
         <v>1614</v>
       </c>
       <c r="B46" s="1">
-        <v>30172</v>
+        <v>30168</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D46" s="1">
         <v>13</v>
@@ -1811,10 +1807,10 @@
         <v>1614</v>
       </c>
       <c r="B47" s="1">
-        <v>30173</v>
+        <v>30169</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D47" s="1">
         <v>13</v>
@@ -1837,10 +1833,10 @@
         <v>1614</v>
       </c>
       <c r="B48" s="1">
-        <v>30174</v>
+        <v>30170</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D48" s="1">
         <v>13</v>
@@ -1849,7 +1845,7 @@
         <v>48</v>
       </c>
       <c r="F48" s="5">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G48" s="3">
         <v>2.5099999999999998</v>
@@ -1860,236 +1856,236 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <v>1633</v>
+        <v>1614</v>
       </c>
       <c r="B49" s="1">
-        <v>9091</v>
+        <v>30171</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D49" s="1">
         <v>13</v>
       </c>
       <c r="E49" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F49" s="5">
-        <v>15000</v>
+        <v>3000</v>
       </c>
       <c r="G49" s="3">
-        <v>1.75</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="H49" s="4">
-        <v>46337</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
-        <v>1633</v>
+        <v>1614</v>
       </c>
       <c r="B50" s="1">
-        <v>30117</v>
+        <v>30172</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="D50" s="1">
         <v>13</v>
       </c>
       <c r="E50" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F50" s="5">
-        <v>15000</v>
+        <v>3000</v>
       </c>
       <c r="G50" s="3">
-        <v>1.75</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="H50" s="4">
-        <v>46337</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <v>1716</v>
+        <v>1614</v>
       </c>
       <c r="B51" s="1">
-        <v>14479</v>
+        <v>30173</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D51" s="1">
         <v>13</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>46</v>
+      <c r="E51" t="s">
+        <v>48</v>
       </c>
       <c r="F51" s="5">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="G51" s="3">
-        <v>2.13</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="H51" s="4">
-        <v>46358</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <v>1716</v>
+        <v>1614</v>
       </c>
       <c r="B52" s="1">
-        <v>14730</v>
+        <v>30174</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D52" s="1">
         <v>13</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>46</v>
+      <c r="E52" t="s">
+        <v>48</v>
       </c>
       <c r="F52" s="5">
         <v>2000</v>
       </c>
       <c r="G52" s="3">
-        <v>2.13</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="H52" s="4">
-        <v>46358</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <v>1716</v>
+        <v>1633</v>
       </c>
       <c r="B53" s="1">
-        <v>17929</v>
+        <v>9091</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D53" s="1">
         <v>13</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>46</v>
+      <c r="E53" t="s">
+        <v>45</v>
       </c>
       <c r="F53" s="5">
         <v>15000</v>
       </c>
       <c r="G53" s="3">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="H53" s="4">
-        <v>46358</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <v>1737</v>
+        <v>1633</v>
       </c>
       <c r="B54" s="1">
-        <v>30104</v>
+        <v>30117</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D54" s="1">
         <v>13</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E54" t="s">
         <v>45</v>
       </c>
       <c r="F54" s="5">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="G54" s="3">
         <v>1.75</v>
       </c>
       <c r="H54" s="4">
-        <v>46364</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
-        <v>1737</v>
+        <v>1716</v>
       </c>
       <c r="B55" s="1">
-        <v>30106</v>
+        <v>14479</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="D55" s="1">
         <v>13</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F55" s="5">
         <v>10000</v>
       </c>
       <c r="G55" s="3">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="H55" s="4">
-        <v>46364</v>
+        <v>46358</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
-        <v>1737</v>
+        <v>1716</v>
       </c>
       <c r="B56" s="1">
-        <v>30107</v>
+        <v>14730</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D56" s="1">
         <v>13</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F56" s="5">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="G56" s="3">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="H56" s="4">
-        <v>46364</v>
+        <v>46358</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <v>1737</v>
+        <v>1716</v>
       </c>
       <c r="B57" s="1">
-        <v>30114</v>
+        <v>17929</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="D57" s="1">
         <v>13</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F57" s="5">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="G57" s="3">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="H57" s="4">
-        <v>46364</v>
+        <v>46358</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
@@ -2097,10 +2093,10 @@
         <v>1737</v>
       </c>
       <c r="B58" s="1">
-        <v>30237</v>
+        <v>30104</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D58" s="1">
         <v>13</v>
@@ -2109,7 +2105,7 @@
         <v>45</v>
       </c>
       <c r="F58" s="5">
-        <v>13000</v>
+        <v>7000</v>
       </c>
       <c r="G58" s="3">
         <v>1.75</v>
@@ -2123,10 +2119,10 @@
         <v>1737</v>
       </c>
       <c r="B59" s="1">
-        <v>30238</v>
+        <v>30106</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="D59" s="1">
         <v>13</v>
@@ -2135,7 +2131,7 @@
         <v>45</v>
       </c>
       <c r="F59" s="5">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G59" s="3">
         <v>1.75</v>
@@ -2149,10 +2145,10 @@
         <v>1737</v>
       </c>
       <c r="B60" s="1">
-        <v>30239</v>
+        <v>30107</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="D60" s="1">
         <v>13</v>
@@ -2161,7 +2157,7 @@
         <v>45</v>
       </c>
       <c r="F60" s="5">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G60" s="3">
         <v>1.75</v>
@@ -2172,136 +2168,166 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
-        <v>1755</v>
+        <v>1737</v>
       </c>
       <c r="B61" s="1">
-        <v>17929</v>
+        <v>30114</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="D61" s="1">
         <v>13</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F61" s="5">
-        <v>14053</v>
+        <v>10000</v>
       </c>
       <c r="G61" s="3">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="H61" s="4">
-        <v>46281</v>
+        <v>46364</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <v>1348</v>
+        <v>1737</v>
       </c>
       <c r="B62" s="1">
-        <v>9091</v>
+        <v>30237</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="D62" s="1">
         <v>13</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F62" s="5">
-        <v>3400</v>
+        <v>13000</v>
       </c>
       <c r="G62" s="3">
-        <v>1.23</v>
+        <v>1.75</v>
       </c>
       <c r="H62" s="4">
-        <v>46268</v>
+        <v>46364</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
-        <v>1348</v>
+        <v>1737</v>
       </c>
       <c r="B63" s="1">
-        <v>30099</v>
+        <v>30238</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D63" s="1">
         <v>13</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F63" s="5">
-        <v>15200</v>
+        <v>5000</v>
       </c>
       <c r="G63" s="3">
-        <v>1.23</v>
+        <v>1.75</v>
       </c>
       <c r="H63" s="4">
-        <v>46176</v>
+        <v>46364</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
-        <v>1348</v>
+        <v>1737</v>
       </c>
       <c r="B64" s="1">
-        <v>30105</v>
+        <v>30239</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="D64" s="1">
         <v>13</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F64" s="5">
-        <v>2400</v>
+        <v>5000</v>
       </c>
       <c r="G64" s="3">
-        <v>1.23</v>
+        <v>1.75</v>
       </c>
       <c r="H64" s="4">
-        <v>46268</v>
+        <v>46364</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
-        <v>1348</v>
+        <v>1769</v>
       </c>
       <c r="B65" s="1">
-        <v>30117</v>
+        <v>30099</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D65" s="1">
         <v>13</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F65" s="5">
-        <v>7000</v>
+        <v>20000</v>
       </c>
       <c r="G65" s="3">
-        <v>1.23</v>
+        <v>1.75</v>
       </c>
       <c r="H65" s="4">
-        <v>46268</v>
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>1769</v>
+      </c>
+      <c r="B66" s="1">
+        <v>30114</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D66" s="1">
+        <v>13</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F66" s="5">
+        <v>10000</v>
+      </c>
+      <c r="G66" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H66" s="4">
+        <v>46371</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H61" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H61" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H65">
+      <sortCondition ref="A1:A61"/>
+    </sortState>
+  </autoFilter>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="9999" orientation="landscape"/>

--- a/data-source/COMPRABASES.xlsx
+++ b/data-source/COMPRABASES.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\SMART-STOCK\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="8_{4387A5D2-32EA-4489-B23A-44C699D43E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{521F6FB8-8B4C-4D5D-906F-728BE9C113A0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC51E46-33C4-4023-8C75-4A244FDD30E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha!$A$1:$H$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha!$A$1:$H$60</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Planilha!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="51">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -81,9 +81,6 @@
     <t>BASE SHANGHAI PU 1.05 - CANELA (COM MARCA D'AGUA)</t>
   </si>
   <si>
-    <t>BASE SHANGHAI PU 1.05 - BORDO (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
     <t>BASE SHANGHAI PU 1.05 - CAFE</t>
   </si>
   <si>
@@ -96,12 +93,6 @@
     <t>BASE SHANGHAI PU 1.05 - CONHAQUE (COM MARCA D'AGUA)</t>
   </si>
   <si>
-    <t>BASE SHANGHAI PU 1.05 - MEL (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - MILITAR (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
     <t>BASE SHANGHAI PU 1.05 - NUDE (COM MARCA D'AGUA)</t>
   </si>
   <si>
@@ -199,9 +190,6 @@
   </si>
   <si>
     <t>BASE SHANGHAI PU 1.05 - GUAVA</t>
-  </si>
-  <si>
-    <t>SHANGHAI</t>
   </si>
 </sst>
 </file>
@@ -593,7 +581,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -645,8 +633,8 @@
       <c r="D2" s="1">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>54</v>
+      <c r="E2" t="s">
+        <v>42</v>
       </c>
       <c r="F2" s="5">
         <v>3356</v>
@@ -671,8 +659,8 @@
       <c r="D3" s="1">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>54</v>
+      <c r="E3" t="s">
+        <v>42</v>
       </c>
       <c r="F3" s="5">
         <v>17467</v>
@@ -697,8 +685,8 @@
       <c r="D4" s="1">
         <v>13</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>54</v>
+      <c r="E4" t="s">
+        <v>42</v>
       </c>
       <c r="F4" s="5">
         <v>2377</v>
@@ -718,13 +706,13 @@
         <v>30117</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1">
         <v>13</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>54</v>
+      <c r="E5" t="s">
+        <v>42</v>
       </c>
       <c r="F5" s="5">
         <v>7098</v>
@@ -750,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F6" s="5">
         <v>30109</v>
@@ -770,13 +758,13 @@
         <v>13485</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D7" s="1">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F7" s="5">
         <v>12298</v>
@@ -796,13 +784,13 @@
         <v>13486</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D8" s="1">
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F8" s="5">
         <v>14386</v>
@@ -828,7 +816,7 @@
         <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F9" s="5">
         <v>590</v>
@@ -848,13 +836,13 @@
         <v>30102</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D10" s="1">
         <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F10" s="5">
         <v>2080</v>
@@ -880,7 +868,7 @@
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F11" s="5">
         <v>415</v>
@@ -906,7 +894,7 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F12" s="5">
         <v>750</v>
@@ -932,7 +920,7 @@
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F13" s="5">
         <v>200</v>
@@ -952,13 +940,13 @@
         <v>30104</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D14" s="1">
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F14" s="5">
         <v>17901</v>
@@ -984,7 +972,7 @@
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F15" s="5">
         <v>1510</v>
@@ -1004,13 +992,13 @@
         <v>30106</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D16" s="1">
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F16" s="5">
         <v>8172</v>
@@ -1036,7 +1024,7 @@
         <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F17" s="5">
         <v>2250</v>
@@ -1062,7 +1050,7 @@
         <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F18" s="5">
         <v>13438</v>
@@ -1082,13 +1070,13 @@
         <v>30108</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D19" s="1">
         <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F19" s="5">
         <v>8083</v>
@@ -1108,13 +1096,13 @@
         <v>30109</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D20" s="1">
         <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F20" s="5">
         <v>5434</v>
@@ -1134,13 +1122,13 @@
         <v>30110</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D21" s="1">
         <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F21" s="5">
         <v>3785</v>
@@ -1154,366 +1142,366 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>1361</v>
+        <v>1471</v>
       </c>
       <c r="B22" s="1">
-        <v>9091</v>
+        <v>30099</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="1">
         <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F22" s="5">
-        <v>11730</v>
+        <v>10111</v>
       </c>
       <c r="G22" s="3">
         <v>1.75</v>
       </c>
       <c r="H22" s="4">
-        <v>46275</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>1361</v>
+        <v>1471</v>
       </c>
       <c r="B23" s="1">
-        <v>30099</v>
+        <v>30107</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D23" s="1">
         <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F23" s="5">
-        <v>5395</v>
+        <v>10128</v>
       </c>
       <c r="G23" s="3">
         <v>1.75</v>
       </c>
       <c r="H23" s="4">
-        <v>46275</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>1361</v>
+        <v>1471</v>
       </c>
       <c r="B24" s="1">
-        <v>30110</v>
+        <v>30114</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D24" s="1">
         <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F24" s="5">
-        <v>2727</v>
+        <v>10103</v>
       </c>
       <c r="G24" s="3">
         <v>1.75</v>
       </c>
       <c r="H24" s="4">
-        <v>46275</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>1361</v>
+        <v>1530</v>
       </c>
       <c r="B25" s="1">
-        <v>30111</v>
+        <v>30099</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D25" s="1">
         <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F25" s="5">
-        <v>7691</v>
+        <v>15000</v>
       </c>
       <c r="G25" s="3">
         <v>1.75</v>
       </c>
       <c r="H25" s="4">
-        <v>46275</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>1361</v>
+        <v>1530</v>
       </c>
       <c r="B26" s="1">
-        <v>30113</v>
+        <v>30114</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D26" s="1">
         <v>13</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F26" s="5">
-        <v>443</v>
+        <v>15000</v>
       </c>
       <c r="G26" s="3">
         <v>1.75</v>
       </c>
       <c r="H26" s="4">
-        <v>46275</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>1361</v>
+        <v>1581</v>
       </c>
       <c r="B27" s="1">
-        <v>30118</v>
+        <v>9091</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D27" s="1">
         <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F27" s="5">
-        <v>2750</v>
+        <v>30000</v>
       </c>
       <c r="G27" s="3">
         <v>1.75</v>
       </c>
       <c r="H27" s="4">
-        <v>46275</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>1471</v>
+        <v>1581</v>
       </c>
       <c r="B28" s="1">
-        <v>30099</v>
+        <v>13485</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D28" s="1">
         <v>13</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F28" s="5">
-        <v>10111</v>
+        <v>25000</v>
       </c>
       <c r="G28" s="3">
         <v>1.75</v>
       </c>
       <c r="H28" s="4">
-        <v>46296</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>1471</v>
+        <v>1581</v>
       </c>
       <c r="B29" s="1">
-        <v>30107</v>
+        <v>14730</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D29" s="1">
         <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F29" s="5">
-        <v>10128</v>
+        <v>5000</v>
       </c>
       <c r="G29" s="3">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="H29" s="4">
-        <v>46296</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>1471</v>
+        <v>1612</v>
       </c>
       <c r="B30" s="1">
-        <v>30114</v>
+        <v>8925</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D30" s="1">
         <v>13</v>
       </c>
       <c r="E30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F30" s="5">
-        <v>10103</v>
+        <v>7000</v>
       </c>
       <c r="G30" s="3">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="H30" s="4">
-        <v>46296</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>1530</v>
+        <v>1612</v>
       </c>
       <c r="B31" s="1">
-        <v>30099</v>
+        <v>30161</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D31" s="1">
         <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F31" s="5">
-        <v>15000</v>
+        <v>3000</v>
       </c>
       <c r="G31" s="3">
-        <v>1.75</v>
+        <v>2.44</v>
       </c>
       <c r="H31" s="4">
-        <v>46217</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>1530</v>
+        <v>1612</v>
       </c>
       <c r="B32" s="1">
-        <v>30114</v>
+        <v>30162</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D32" s="1">
         <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F32" s="5">
-        <v>15000</v>
+        <v>3000</v>
       </c>
       <c r="G32" s="3">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="H32" s="4">
-        <v>46217</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <v>1581</v>
+        <v>1612</v>
       </c>
       <c r="B33" s="1">
-        <v>9091</v>
+        <v>30163</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D33" s="1">
         <v>13</v>
       </c>
       <c r="E33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F33" s="5">
-        <v>30000</v>
+        <v>3000</v>
       </c>
       <c r="G33" s="3">
-        <v>1.75</v>
+        <v>2.44</v>
       </c>
       <c r="H33" s="4">
-        <v>46324</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <v>1581</v>
+        <v>1612</v>
       </c>
       <c r="B34" s="1">
-        <v>13485</v>
+        <v>30164</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D34" s="1">
         <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F34" s="5">
-        <v>25000</v>
+        <v>3000</v>
       </c>
       <c r="G34" s="3">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="H34" s="4">
-        <v>46324</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <v>1581</v>
+        <v>1612</v>
       </c>
       <c r="B35" s="1">
-        <v>14730</v>
+        <v>30165</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D35" s="1">
         <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F35" s="5">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="G35" s="3">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="H35" s="4">
-        <v>46324</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -1521,19 +1509,19 @@
         <v>1612</v>
       </c>
       <c r="B36" s="1">
-        <v>8925</v>
+        <v>30166</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D36" s="1">
         <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F36" s="5">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="G36" s="3">
         <v>2.6</v>
@@ -1544,25 +1532,25 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="B37" s="1">
-        <v>30161</v>
+        <v>12494</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D37" s="1">
         <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F37" s="5">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="G37" s="3">
-        <v>2.44</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="H37" s="4">
         <v>46332</v>
@@ -1570,25 +1558,25 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="B38" s="1">
-        <v>30162</v>
+        <v>12495</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D38" s="1">
         <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F38" s="5">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G38" s="3">
-        <v>2.6</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="H38" s="4">
         <v>46332</v>
@@ -1596,25 +1584,25 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="B39" s="1">
-        <v>30163</v>
+        <v>30167</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D39" s="1">
         <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F39" s="5">
         <v>3000</v>
       </c>
       <c r="G39" s="3">
-        <v>2.44</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="H39" s="4">
         <v>46332</v>
@@ -1622,25 +1610,25 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="B40" s="1">
-        <v>30164</v>
+        <v>30168</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D40" s="1">
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F40" s="5">
         <v>3000</v>
       </c>
       <c r="G40" s="3">
-        <v>2.6</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="H40" s="4">
         <v>46332</v>
@@ -1648,25 +1636,25 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="B41" s="1">
-        <v>30165</v>
+        <v>30169</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D41" s="1">
         <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F41" s="5">
         <v>3000</v>
       </c>
       <c r="G41" s="3">
-        <v>2.6</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="H41" s="4">
         <v>46332</v>
@@ -1674,25 +1662,25 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="B42" s="1">
-        <v>30166</v>
+        <v>30170</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D42" s="1">
         <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F42" s="5">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="G42" s="3">
-        <v>2.6</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="H42" s="4">
         <v>46332</v>
@@ -1703,19 +1691,19 @@
         <v>1614</v>
       </c>
       <c r="B43" s="1">
-        <v>12494</v>
+        <v>30171</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D43" s="1">
         <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F43" s="5">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="G43" s="3">
         <v>2.5099999999999998</v>
@@ -1729,19 +1717,19 @@
         <v>1614</v>
       </c>
       <c r="B44" s="1">
-        <v>12495</v>
+        <v>30172</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D44" s="1">
         <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F44" s="5">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G44" s="3">
         <v>2.5099999999999998</v>
@@ -1755,16 +1743,16 @@
         <v>1614</v>
       </c>
       <c r="B45" s="1">
-        <v>30167</v>
+        <v>30173</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D45" s="1">
         <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F45" s="5">
         <v>3000</v>
@@ -1781,19 +1769,19 @@
         <v>1614</v>
       </c>
       <c r="B46" s="1">
-        <v>30168</v>
+        <v>30174</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D46" s="1">
         <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F46" s="5">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G46" s="3">
         <v>2.5099999999999998</v>
@@ -1804,288 +1792,288 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
-        <v>1614</v>
+        <v>1633</v>
       </c>
       <c r="B47" s="1">
-        <v>30169</v>
+        <v>9091</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="D47" s="1">
         <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F47" s="5">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="G47" s="3">
-        <v>2.5099999999999998</v>
+        <v>1.75</v>
       </c>
       <c r="H47" s="4">
-        <v>46332</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
-        <v>1614</v>
+        <v>1633</v>
       </c>
       <c r="B48" s="1">
-        <v>30170</v>
+        <v>30117</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D48" s="1">
         <v>13</v>
       </c>
       <c r="E48" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F48" s="5">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="G48" s="3">
-        <v>2.5099999999999998</v>
+        <v>1.75</v>
       </c>
       <c r="H48" s="4">
-        <v>46332</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <v>1614</v>
+        <v>1716</v>
       </c>
       <c r="B49" s="1">
-        <v>30171</v>
+        <v>14479</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D49" s="1">
         <v>13</v>
       </c>
-      <c r="E49" t="s">
-        <v>48</v>
+      <c r="E49" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F49" s="5">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="G49" s="3">
-        <v>2.5099999999999998</v>
+        <v>2.13</v>
       </c>
       <c r="H49" s="4">
-        <v>46332</v>
+        <v>46358</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
-        <v>1614</v>
+        <v>1716</v>
       </c>
       <c r="B50" s="1">
-        <v>30172</v>
+        <v>14730</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D50" s="1">
         <v>13</v>
       </c>
-      <c r="E50" t="s">
-        <v>48</v>
+      <c r="E50" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F50" s="5">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G50" s="3">
-        <v>2.5099999999999998</v>
+        <v>2.13</v>
       </c>
       <c r="H50" s="4">
-        <v>46332</v>
+        <v>46358</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <v>1614</v>
+        <v>1716</v>
       </c>
       <c r="B51" s="1">
-        <v>30173</v>
+        <v>17929</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D51" s="1">
+        <v>13</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D51" s="1">
-        <v>13</v>
-      </c>
-      <c r="E51" t="s">
-        <v>48</v>
-      </c>
       <c r="F51" s="5">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="G51" s="3">
-        <v>2.5099999999999998</v>
+        <v>2.13</v>
       </c>
       <c r="H51" s="4">
-        <v>46332</v>
+        <v>46358</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <v>1614</v>
+        <v>1737</v>
       </c>
       <c r="B52" s="1">
-        <v>30174</v>
+        <v>30104</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="D52" s="1">
         <v>13</v>
       </c>
-      <c r="E52" t="s">
-        <v>48</v>
+      <c r="E52" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="F52" s="5">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="G52" s="3">
-        <v>2.5099999999999998</v>
+        <v>1.75</v>
       </c>
       <c r="H52" s="4">
-        <v>46332</v>
+        <v>46364</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <v>1633</v>
+        <v>1737</v>
       </c>
       <c r="B53" s="1">
-        <v>9091</v>
+        <v>30106</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D53" s="1">
         <v>13</v>
       </c>
-      <c r="E53" t="s">
-        <v>45</v>
+      <c r="E53" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="F53" s="5">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="G53" s="3">
         <v>1.75</v>
       </c>
       <c r="H53" s="4">
-        <v>46337</v>
+        <v>46364</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <v>1633</v>
+        <v>1737</v>
       </c>
       <c r="B54" s="1">
-        <v>30117</v>
+        <v>30107</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D54" s="1">
         <v>13</v>
       </c>
-      <c r="E54" t="s">
-        <v>45</v>
+      <c r="E54" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="F54" s="5">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="G54" s="3">
         <v>1.75</v>
       </c>
       <c r="H54" s="4">
-        <v>46337</v>
+        <v>46364</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
-        <v>1716</v>
+        <v>1737</v>
       </c>
       <c r="B55" s="1">
-        <v>14479</v>
+        <v>30114</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="D55" s="1">
         <v>13</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F55" s="5">
         <v>10000</v>
       </c>
       <c r="G55" s="3">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="H55" s="4">
-        <v>46358</v>
+        <v>46364</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
-        <v>1716</v>
+        <v>1737</v>
       </c>
       <c r="B56" s="1">
-        <v>14730</v>
+        <v>30237</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D56" s="1">
         <v>13</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F56" s="5">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="G56" s="3">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="H56" s="4">
-        <v>46358</v>
+        <v>46364</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <v>1716</v>
+        <v>1737</v>
       </c>
       <c r="B57" s="1">
-        <v>17929</v>
+        <v>30238</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D57" s="1">
         <v>13</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F57" s="5">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="G57" s="3">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="H57" s="4">
-        <v>46358</v>
+        <v>46364</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
@@ -2093,19 +2081,19 @@
         <v>1737</v>
       </c>
       <c r="B58" s="1">
-        <v>30104</v>
+        <v>30239</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="D58" s="1">
         <v>13</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F58" s="5">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="G58" s="3">
         <v>1.75</v>
@@ -2116,45 +2104,45 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
-        <v>1737</v>
+        <v>1769</v>
       </c>
       <c r="B59" s="1">
-        <v>30106</v>
+        <v>30099</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D59" s="1">
         <v>13</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F59" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="G59" s="3">
         <v>1.75</v>
       </c>
       <c r="H59" s="4">
-        <v>46364</v>
+        <v>46371</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
-        <v>1737</v>
+        <v>1769</v>
       </c>
       <c r="B60" s="1">
-        <v>30107</v>
+        <v>30114</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D60" s="1">
         <v>13</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F60" s="5">
         <v>10000</v>
@@ -2163,169 +2151,13 @@
         <v>1.75</v>
       </c>
       <c r="H60" s="4">
-        <v>46364</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="1">
-        <v>1737</v>
-      </c>
-      <c r="B61" s="1">
-        <v>30114</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D61" s="1">
-        <v>13</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F61" s="5">
-        <v>10000</v>
-      </c>
-      <c r="G61" s="3">
-        <v>1.75</v>
-      </c>
-      <c r="H61" s="4">
-        <v>46364</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="1">
-        <v>1737</v>
-      </c>
-      <c r="B62" s="1">
-        <v>30237</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D62" s="1">
-        <v>13</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F62" s="5">
-        <v>13000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1.75</v>
-      </c>
-      <c r="H62" s="4">
-        <v>46364</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="1">
-        <v>1737</v>
-      </c>
-      <c r="B63" s="1">
-        <v>30238</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D63" s="1">
-        <v>13</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F63" s="5">
-        <v>5000</v>
-      </c>
-      <c r="G63" s="3">
-        <v>1.75</v>
-      </c>
-      <c r="H63" s="4">
-        <v>46364</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="1">
-        <v>1737</v>
-      </c>
-      <c r="B64" s="1">
-        <v>30239</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D64" s="1">
-        <v>13</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F64" s="5">
-        <v>5000</v>
-      </c>
-      <c r="G64" s="3">
-        <v>1.75</v>
-      </c>
-      <c r="H64" s="4">
-        <v>46364</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="1">
-        <v>1769</v>
-      </c>
-      <c r="B65" s="1">
-        <v>30099</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="1">
-        <v>13</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F65" s="5">
-        <v>20000</v>
-      </c>
-      <c r="G65" s="3">
-        <v>1.75</v>
-      </c>
-      <c r="H65" s="4">
         <v>46371</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="1">
-        <v>1769</v>
-      </c>
-      <c r="B66" s="1">
-        <v>30114</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D66" s="1">
-        <v>13</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F66" s="5">
-        <v>10000</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1.75</v>
-      </c>
-      <c r="H66" s="4">
-        <v>46371</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H61" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H65">
-      <sortCondition ref="A1:A61"/>
+  <autoFilter ref="A1:H60" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H59">
+      <sortCondition ref="A1:A55"/>
     </sortState>
   </autoFilter>
   <printOptions gridLines="1"/>

--- a/data-source/COMPRABASES.xlsx
+++ b/data-source/COMPRABASES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\SMART-STOCK\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC51E46-33C4-4023-8C75-4A244FDD30E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9A1EA1-33D3-4A24-880D-65042B7C2076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="51">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -581,7 +581,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -2154,6 +2154,84 @@
         <v>46371</v>
       </c>
     </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>1812</v>
+      </c>
+      <c r="B61" s="1">
+        <v>9091</v>
+      </c>
+      <c r="C61" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="1">
+        <v>13</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F61" s="5">
+        <v>5000</v>
+      </c>
+      <c r="G61" s="3">
+        <v>1.84</v>
+      </c>
+      <c r="H61" s="4">
+        <v>46378</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>1812</v>
+      </c>
+      <c r="B62" s="1">
+        <v>30099</v>
+      </c>
+      <c r="C62" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="1">
+        <v>13</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F62" s="5">
+        <v>15000</v>
+      </c>
+      <c r="G62" s="3">
+        <v>1.84</v>
+      </c>
+      <c r="H62" s="4">
+        <v>46378</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>1812</v>
+      </c>
+      <c r="B63" s="1">
+        <v>30102</v>
+      </c>
+      <c r="C63" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" s="1">
+        <v>13</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F63" s="5">
+        <v>10000</v>
+      </c>
+      <c r="G63" s="3">
+        <v>1.84</v>
+      </c>
+      <c r="H63" s="4">
+        <v>46378</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H60" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H59">
